--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484864_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484864_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2778</v>
+        <v>7.2243</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9729</v>
+        <v>8.6549</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6951</v>
+        <v>-1.4306</v>
       </c>
       <c r="G2" t="n">
         <v>6.7363</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.723</v>
+        <v>-0.7764</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7519</v>
+        <v>-0.0699</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9711</v>
+        <v>-0.7065</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6226</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7476</v>
+        <v>4.9354</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3846</v>
+        <v>3.9692</v>
       </c>
       <c r="F3" t="n">
-        <v>1.363</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>2.5403</v>
@@ -688,13 +688,13 @@
         <v>2.6418</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4344</v>
+        <v>-0.2466</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3963</v>
+        <v>0.1883</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0381</v>
+        <v>-0.4349</v>
       </c>
       <c r="V3" t="n">
         <v>0.9434</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3093</v>
+        <v>3.4059</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3665</v>
+        <v>2.4896</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9428</v>
+        <v>0.9163</v>
       </c>
       <c r="G4" t="n">
         <v>3.7719</v>
@@ -766,13 +766,13 @@
         <v>1.6983</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3867</v>
+        <v>0.4834</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5031</v>
+        <v>0.6261</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1163</v>
+        <v>-0.1428</v>
       </c>
       <c r="V4" t="n">
         <v>0.2828</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2985</v>
+        <v>3.05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4646</v>
+        <v>4.2954</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1661</v>
+        <v>-1.2454</v>
       </c>
       <c r="G5" t="n">
         <v>1.6804</v>
@@ -844,13 +844,13 @@
         <v>2.0757</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7876</v>
+        <v>0.5391</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1403</v>
+        <v>0.9711</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3526</v>
+        <v>-0.432</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2452</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7701</v>
+        <v>1.9985</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7493</v>
+        <v>2.5545</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9792999999999999</v>
+        <v>-0.556</v>
       </c>
       <c r="G6" t="n">
         <v>2.1368</v>
@@ -922,13 +922,13 @@
         <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-0.761</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4296</v>
+        <v>0.2348</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.419</v>
+        <v>-0.9957</v>
       </c>
       <c r="V6" t="n">
         <v>0.6226</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3999</v>
+        <v>1.6393</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2183</v>
+        <v>1.5106</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1817</v>
+        <v>0.1288</v>
       </c>
       <c r="G7" t="n">
         <v>1.713</v>
@@ -1000,13 +1000,13 @@
         <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3321</v>
+        <v>-0.0927</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3281</v>
+        <v>-0.0357</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0041</v>
+        <v>-0.057</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9244</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6489</v>
+        <v>1.0483</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5293</v>
+        <v>1.1139</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1196</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>2.5821</v>
@@ -1078,13 +1078,13 @@
         <v>1.5096</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.3906</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3404</v>
+        <v>0.2442</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3316</v>
+        <v>0.1464</v>
       </c>
       <c r="V8" t="n">
         <v>-1.547</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1196</v>
+        <v>0.2171</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2575</v>
+        <v>1.355</v>
       </c>
       <c r="F9" t="n">
         <v>-1.1379</v>
@@ -1156,10 +1156,10 @@
         <v>0.1887</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0123</v>
+        <v>0.1098</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0123</v>
+        <v>0.1098</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>P. HURYNOWICZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6541</v>
+        <v>-1.082</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0623</v>
+        <v>-1.1894</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4083</v>
+        <v>0.1073</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3331</v>
+        <v>-1.3805</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0211</v>
+        <v>-0.8609</v>
       </c>
       <c r="I10" t="n">
-        <v>0.312</v>
+        <v>-0.5196</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2209</v>
+        <v>-1.2991</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0259</v>
+        <v>-0.6496</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2468</v>
+        <v>-0.6496</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1122</v>
+        <v>-0.0814</v>
       </c>
       <c r="N10" t="n">
-        <v>0.047</v>
+        <v>-0.2113</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.1299</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2644</v>
+        <v>0.1887</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.774</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>1.579</v>
+        <v>0.1098</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4907</v>
+        <v>0.1098</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0883</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. HURYNOWICZ</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1795</v>
+        <v>-1.7426</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2868</v>
+        <v>-2.9393</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1073</v>
+        <v>1.1966</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3805</v>
+        <v>0.3331</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8609</v>
+        <v>0.0211</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5196</v>
+        <v>0.312</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2991</v>
+        <v>0.2209</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6496</v>
+        <v>-0.0259</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6496</v>
+        <v>0.2468</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0814</v>
+        <v>0.1122</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2113</v>
+        <v>0.047</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1299</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1887</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1887</v>
+        <v>1.5096</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0123</v>
+        <v>0.4904</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0123</v>
+        <v>0.6138</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0.1234</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8346</v>
+        <v>-2.1125</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5591</v>
+        <v>-1.5645</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2755</v>
+        <v>-0.548</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6744</v>
+        <v>-2.5448</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0816</v>
+        <v>-1.3907</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5929</v>
+        <v>-1.1542</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0596</v>
+        <v>-1.5736</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1049</v>
+        <v>-0.3326</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1645</v>
+        <v>-1.241</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.734</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9767</v>
+        <v>-1.058</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7574</v>
+        <v>0.0868</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9435</v>
+        <v>1.5096</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5185</v>
+        <v>-0.4547</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.09</v>
+        <v>0.0091</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4285</v>
+        <v>-0.4638</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3018</v>
+        <v>-0.6226</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9088</v>
+        <v>-2.5868</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1491</v>
+        <v>-2.3642</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7597</v>
+        <v>-0.2226</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.5448</v>
+        <v>-1.6744</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3907</v>
+        <v>-1.0816</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1542</v>
+        <v>-0.5929</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.5736</v>
+        <v>0.0596</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3326</v>
+        <v>-0.1049</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.241</v>
+        <v>0.1645</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-1.734</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.058</v>
+        <v>-0.9767</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0868</v>
+        <v>-0.7574</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5096</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2509</v>
+        <v>-0.2707</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5755</v>
+        <v>0.1049</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6754</v>
+        <v>-0.3756</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6226</v>
+        <v>0.3018</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.9947</v>
+        <v>15.9949</v>
       </c>
       <c r="E14" t="n">
         <v>17.8857</v>
@@ -1528,7 +1528,7 @@
         <v>6.274500000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.516299999999999</v>
+        <v>-8.516300000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-5.0554</v>
@@ -1546,13 +1546,13 @@
         <v>17.9265</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4791999999999996</v>
+        <v>-0.479</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1061</v>
+        <v>3.1063</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.5852</v>
+        <v>-3.5853</v>
       </c>
       <c r="V14" t="n">
         <v>-3.113</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5732</v>
+        <v>3.1261</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0786</v>
+        <v>3.4222</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5054</v>
+        <v>-0.2961</v>
       </c>
       <c r="G15" t="n">
         <v>0.4824</v>
@@ -1624,13 +1624,13 @@
         <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2984</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>2.567</v>
+        <v>0.9106</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2686</v>
+        <v>-0.0593</v>
       </c>
       <c r="V15" t="n">
         <v>0.2828</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. MARCO CLIMENT</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2815</v>
+        <v>-0.8546</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7419</v>
+        <v>0.8374</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0234</v>
+        <v>-1.692</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.53</v>
+        <v>-0.7995</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9978</v>
+        <v>0.0337</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5322</v>
+        <v>-0.8331</v>
       </c>
       <c r="J17" t="n">
-        <v>2.095</v>
+        <v>0.7448</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2638</v>
+        <v>0.5392</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.2057</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.6249</v>
+        <v>-1.5443</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.2617</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3633</v>
+        <v>-1.0388</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.3966</v>
+        <v>0.7548</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.2836</v>
+        <v>-0.3774</v>
       </c>
       <c r="R17" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8452</v>
+        <v>0.239</v>
       </c>
       <c r="T17" t="n">
-        <v>3.0061</v>
+        <v>0.4699</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.161</v>
+        <v>-0.231</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7999000000000001</v>
+        <v>-1.0489</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1245</v>
+        <v>-1.0489</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FONT FENOLLAR</t>
+          <t>E. MORATA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3127</v>
+        <v>-0.8963</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5613</v>
+        <v>-0.1919</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8741</v>
+        <v>-0.7043</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9947</v>
+        <v>-4.3026</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0102</v>
+        <v>-3.6054</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0049</v>
+        <v>-0.6972</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9404</v>
+        <v>-2.0264</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8241000000000001</v>
+        <v>-1.3938</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1163</v>
+        <v>-0.6325</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9351</v>
+        <v>-2.2763</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8139</v>
+        <v>-2.2116</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1212</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1322</v>
+        <v>-0.1887</v>
       </c>
       <c r="R18" t="n">
         <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5143</v>
+        <v>0.1987</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4921</v>
+        <v>0.4761</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0223</v>
+        <v>-0.2774</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8189</v>
+        <v>1.8868</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2452</v>
+        <v>1.547</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4263</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>A. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4416</v>
+        <v>-0.9013</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6425</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0841</v>
+        <v>-1.8523</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7995</v>
+        <v>-1.9947</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0337</v>
+        <v>0.0102</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8331</v>
+        <v>-2.0049</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7448</v>
+        <v>0.9404</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5392</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2057</v>
+        <v>0.1163</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5443</v>
+        <v>-2.9351</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.8139</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0388</v>
+        <v>-2.1212</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.3774</v>
+        <v>-1.1322</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.348</v>
+        <v>-0.1029</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2751</v>
+        <v>-0.1023</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6231</v>
+        <v>-0.0005</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0489</v>
+        <v>0.8189</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0489</v>
+        <v>-0.4263</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. MORATA</t>
+          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4424</v>
+        <v>-1.0392</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5817</v>
+        <v>0.4911</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8607</v>
+        <v>-1.5303</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.3026</v>
+        <v>0.8433</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.6054</v>
+        <v>0.3537</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6972</v>
+        <v>0.4896</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.0264</v>
+        <v>3.8338</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3938</v>
+        <v>2.4354</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6325</v>
+        <v>1.3984</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2763</v>
+        <v>-2.9905</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2116</v>
+        <v>-2.0817</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.9089</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3209</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1887</v>
+        <v>-3.0192</v>
       </c>
       <c r="R20" t="n">
         <v>1.5096</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3474</v>
+        <v>-0.5692</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0864</v>
+        <v>-0.3235</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4338</v>
+        <v>-0.2457</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8868</v>
+        <v>0.1963</v>
       </c>
       <c r="W20" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3398</v>
+        <v>0.1963</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5877</v>
+        <v>-1.8598</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7272</v>
+        <v>3.0525</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1394</v>
+        <v>-4.9123</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4525</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1927</v>
+        <v>-1.4188</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2598</v>
+        <v>1.3247</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2569</v>
+        <v>3.6235</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6073</v>
+        <v>1.6066</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6496</v>
+        <v>2.0168</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1956</v>
+        <v>-3.7176</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5854</v>
+        <v>-3.0255</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3897</v>
+        <v>-0.6922</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1322</v>
+        <v>-2.4531</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1887</v>
+        <v>2.4531</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8083</v>
+        <v>-0.0751</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6619</v>
+        <v>0.3351</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1464</v>
+        <v>-0.4102</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.6905</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-3.2375</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7333</v>
+        <v>-2.0039</v>
       </c>
       <c r="E22" t="n">
-        <v>0.004</v>
+        <v>-2.1169</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7373</v>
+        <v>0.113</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8433</v>
+        <v>-1.4525</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3537</v>
+        <v>-1.1927</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4896</v>
+        <v>-0.2598</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8338</v>
+        <v>-1.2569</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4354</v>
+        <v>-0.6073</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3984</v>
+        <v>-0.6496</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.9905</v>
+        <v>-0.1956</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.0817</v>
+        <v>-0.5854</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9089</v>
+        <v>0.3897</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5096</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.0192</v>
+        <v>-1.1322</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2633</v>
+        <v>0.3921</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8107</v>
+        <v>0.2722</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4526</v>
+        <v>0.1199</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1963</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>F. MARCO CLIMENT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8688</v>
+        <v>-2.9343</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0363</v>
+        <v>-1.0119</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8325</v>
+        <v>-1.9223</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.7964</v>
+        <v>-1.53</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.7962</v>
+        <v>-0.9978</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0002</v>
+        <v>-0.5322</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1691</v>
+        <v>2.095</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6018</v>
+        <v>1.2638</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5673</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6273</v>
+        <v>-3.6249</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.1944</v>
+        <v>-2.2617</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4329</v>
+        <v>-1.3633</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9435</v>
+        <v>-3.3966</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-5.2836</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9435</v>
+        <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0159</v>
+        <v>1.1924</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1328</v>
+        <v>1.2523</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1487</v>
+        <v>-0.0599</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9491</v>
+        <v>-3.0131</v>
       </c>
       <c r="E24" t="n">
-        <v>1.591</v>
+        <v>-1.2312</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.5401</v>
+        <v>-1.7819</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-3.7964</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4188</v>
+        <v>-2.7962</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3247</v>
+        <v>-1.0002</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6235</v>
+        <v>-1.1691</v>
       </c>
       <c r="K24" t="n">
-        <v>1.6066</v>
+        <v>-0.6018</v>
       </c>
       <c r="L24" t="n">
-        <v>2.0168</v>
+        <v>-0.5673</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.7176</v>
+        <v>-2.6273</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.0255</v>
+        <v>-2.1944</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6922</v>
+        <v>-0.4329</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4531</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4531</v>
+        <v>0.9435</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.1645</v>
+        <v>-0.1602</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1264</v>
+        <v>-0.0621</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0381</v>
+        <v>-0.0982</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.6905</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.2375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8356</v>
+        <v>-5.5545</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.2679</v>
+        <v>-4.1961</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5677</v>
+        <v>-1.3584</v>
       </c>
       <c r="G25" t="n">
         <v>-5.0534</v>
@@ -2404,13 +2404,13 @@
         <v>1.3209</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8195</v>
+        <v>0.4616</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7149</v>
+        <v>0.3569</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1046</v>
+        <v>0.1047</v>
       </c>
       <c r="V25" t="n">
         <v>1.8678</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.9947</v>
+        <v>-14.0461</v>
       </c>
       <c r="E26" t="n">
-        <v>1.891000000000001</v>
+        <v>1.891100000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-17.8859</v>
+        <v>-15.9369</v>
       </c>
       <c r="G26" t="n">
         <v>-15.8128</v>
@@ -2455,10 +2455,10 @@
         <v>-2.8139</v>
       </c>
       <c r="J26" t="n">
-        <v>8.516099999999998</v>
+        <v>8.516100000000002</v>
       </c>
       <c r="K26" t="n">
-        <v>5.055300000000002</v>
+        <v>5.0553</v>
       </c>
       <c r="L26" t="n">
         <v>3.460799999999999</v>
@@ -2470,7 +2470,7 @@
         <v>-18.0543</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.2749</v>
+        <v>-6.274900000000001</v>
       </c>
       <c r="P26" t="n">
         <v>-3.774</v>
@@ -2482,19 +2482,19 @@
         <v>14.1525</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4790000000000006</v>
+        <v>2.4277</v>
       </c>
       <c r="T26" t="n">
         <v>3.585199999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.1064</v>
+        <v>-1.1576</v>
       </c>
       <c r="V26" t="n">
         <v>3.1131</v>
       </c>
       <c r="W26" t="n">
-        <v>7.715999999999999</v>
+        <v>7.716</v>
       </c>
       <c r="X26" t="n">
         <v>-4.6029</v>
